--- a/data/satisfaction_detail/2026/1-8月/会议主承办.xlsx
+++ b/data/satisfaction_detail/2026/1-8月/会议主承办.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.52</v>
+        <v>9.667537800413816</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.56</v>
+        <v>9.783895166852353</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.890000000000001</v>
+        <v>9.890846198737334</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9.9</v>
+        <v>9.897813146586026</v>
       </c>
     </row>
     <row r="4">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.94</v>
+        <v>9.945074009231259</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>10</v>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9.91</v>
+        <v>9.918558013687729</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>10</v>
@@ -527,7 +527,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.97348400445647</v>
       </c>
     </row>
     <row r="7">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9.91</v>
+        <v>9.917926680460502</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.91</v>
+        <v>9.917295347233274</v>
       </c>
     </row>
     <row r="8">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.969361769855166</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.710000000000001</v>
+        <v>9.705806143561993</v>
       </c>
     </row>
     <row r="9">
@@ -566,7 +566,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.97348400445647</v>
       </c>
     </row>
     <row r="10">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.94</v>
+        <v>9.945074009231259</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.91</v>
+        <v>9.918558013687729</v>
       </c>
     </row>
     <row r="11">
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>9.83</v>
+        <v>9.853241020743807</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.83</v>
+        <v>9.857281553398058</v>
       </c>
     </row>
     <row r="12">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.76</v>
+        <v>9.691233487187649</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.737068279484324</v>
       </c>
     </row>
     <row r="13">
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.83</v>
+        <v>9.82259536314924</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.83</v>
+        <v>9.865526022600669</v>
       </c>
     </row>
     <row r="14">
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.82</v>
+        <v>9.810265796593983</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.85</v>
+        <v>9.853196456045413</v>
       </c>
     </row>
     <row r="15">
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9.859999999999999</v>
+        <v>9.843681892938617</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>9.91</v>
+        <v>9.918558013687729</v>
       </c>
     </row>
     <row r="16">
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>9.91</v>
+        <v>9.914435779086425</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.807109130457849</v>
       </c>
     </row>
     <row r="17">
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.806477797230624</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.887919783542895</v>
       </c>
     </row>
     <row r="18">
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>9.91</v>
+        <v>9.917295347233274</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.97348400445647</v>
       </c>
     </row>
     <row r="19">
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.889516685235291</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.97348400445647</v>
       </c>
     </row>
     <row r="20">
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>9.49</v>
+        <v>9.52103665976975</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>9.779999999999999</v>
+        <v>9.793633614515359</v>
       </c>
     </row>
     <row r="21">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>9.43</v>
+        <v>9.449411639874794</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.892042018144199</v>
       </c>
     </row>
     <row r="22">
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>9.17</v>
+        <v>9.254634728632819</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.804249562310998</v>
       </c>
     </row>
     <row r="23">
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>9.57</v>
+        <v>9.59701787893257</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.805764762056343</v>
       </c>
     </row>
     <row r="24">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>9.43</v>
+        <v>9.461117300652555</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>9.859999999999999</v>
+        <v>9.87120802164571</v>
       </c>
     </row>
     <row r="25">
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>9.73</v>
+        <v>9.763807098519816</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>9.58</v>
+        <v>9.594609793623006</v>
       </c>
     </row>
     <row r="26">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>9.529999999999999</v>
+        <v>9.530728420605868</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>9.85</v>
+        <v>9.861403787999365</v>
       </c>
     </row>
     <row r="27">
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>9.69</v>
+        <v>9.732420287548411</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>9.69</v>
+        <v>9.718441827152635</v>
       </c>
     </row>
     <row r="28">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>9.34</v>
+        <v>9.363803915327072</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.800588360125207</v>
       </c>
     </row>
     <row r="29">
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.684420393654836</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>9.789999999999999</v>
+        <v>9.7449116664014</v>
       </c>
     </row>
     <row r="30">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>9.07</v>
+        <v>9.05794790174545</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>9.59</v>
+        <v>9.606308026951032</v>
       </c>
     </row>
     <row r="31">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>9.94</v>
+        <v>9.968341495858276</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.784146562670053</v>
       </c>
     </row>
     <row r="32">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>9.84</v>
+        <v>9.817507560082763</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.810600031831928</v>
       </c>
     </row>
     <row r="33">
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>9.94</v>
+        <v>9.949872141758185</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.772467504907423</v>
       </c>
     </row>
     <row r="34">
